--- a/backend/data/financials_by_company/002294.SZ.xlsx
+++ b/backend/data/financials_by_company/002294.SZ.xlsx
@@ -682,634 +682,634 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-8221788.181347</v>
+        <v>-18621903.553366</v>
       </c>
       <c r="C2" t="n">
-        <v>0.043257</v>
+        <v>0.119232</v>
       </c>
       <c r="D2" t="n">
-        <v>1214991466.4</v>
+        <v>1070819320.53</v>
       </c>
       <c r="E2" t="n">
-        <v>-190069745.95</v>
+        <v>-156182639.1</v>
       </c>
       <c r="F2" t="n">
-        <v>-190069745.95</v>
+        <v>-156182639.1</v>
       </c>
       <c r="G2" t="n">
-        <v>601569140.2</v>
+        <v>533726576.95</v>
       </c>
       <c r="H2" t="n">
-        <v>376231728.48</v>
+        <v>304268219.64</v>
       </c>
       <c r="I2" t="n">
-        <v>1097553475.04</v>
+        <v>793279487.98</v>
       </c>
       <c r="J2" t="n">
-        <v>1024921720.45</v>
+        <v>914636681.4299999</v>
       </c>
       <c r="K2" t="n">
-        <v>648689991.97</v>
+        <v>610368461.79</v>
       </c>
       <c r="L2" t="n">
-        <v>30475527.21</v>
+        <v>36778357.6</v>
       </c>
       <c r="M2" t="n">
-        <v>16173784.9</v>
+        <v>10526880.76</v>
       </c>
       <c r="N2" t="n">
-        <v>47064122.34</v>
+        <v>47658560.86</v>
       </c>
       <c r="O2" t="n">
-        <v>783417097.968653</v>
+        <v>671287312.496634</v>
       </c>
       <c r="P2" t="n">
-        <v>601569140.2</v>
+        <v>533726576.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>3241039750.43</v>
+        <v>2481247767.46</v>
       </c>
       <c r="R2" t="n">
-        <v>646309880.85</v>
+        <v>586195029.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1114016926</v>
+        <v>1067453154</v>
       </c>
       <c r="T2" t="n">
-        <v>1114016926</v>
+        <v>1067453154</v>
       </c>
       <c r="U2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="n">
-        <v>601569140.2</v>
+        <v>533726576.95</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>601569140.2</v>
+        <v>533726576.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>-3586509.04</v>
+        <v>5405058.16</v>
       </c>
       <c r="AA2" t="n">
-        <v>605155649.24</v>
+        <v>528321518.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>605155649.24</v>
+        <v>528321518.79</v>
       </c>
       <c r="AC2" t="n">
-        <v>27360557.83</v>
+        <v>71520062.23999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>632516207.0700001</v>
+        <v>599841581.03</v>
       </c>
       <c r="AE2" t="n">
-        <v>-13793673.78</v>
+        <v>13646551.79</v>
       </c>
       <c r="AF2" t="n">
-        <v>-204582703.96</v>
+        <v>-156182639.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>148625.82</v>
+        <v>1296526.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>6442945</v>
+        <v>7623146.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>197991133.14</v>
+        <v>147262966.52</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30475527.21</v>
+        <v>36778357.6</v>
       </c>
       <c r="AK2" t="n">
-        <v>414810.23</v>
+        <v>353322.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>16173784.9</v>
+        <v>10526880.76</v>
       </c>
       <c r="AM2" t="n">
-        <v>47064122.34</v>
+        <v>47658560.86</v>
       </c>
       <c r="AN2" t="n">
-        <v>771191842.96</v>
+        <v>577144273.91</v>
       </c>
       <c r="AO2" t="n">
-        <v>2143486275.39</v>
+        <v>1687968279.48</v>
       </c>
       <c r="AP2" t="n">
-        <v>50865074.41</v>
+        <v>44978643.62</v>
       </c>
       <c r="AQ2" t="n">
-        <v>33763392.05</v>
+        <v>134235745.19</v>
       </c>
       <c r="AR2" t="n">
-        <v>33763392.05</v>
+        <v>134235745.19</v>
       </c>
       <c r="AS2" t="n">
-        <v>421239678.51</v>
+        <v>357368428.49</v>
       </c>
       <c r="AT2" t="n">
-        <v>1061874132.18</v>
+        <v>673634457.9400001</v>
       </c>
       <c r="AU2" t="n">
-        <v>980416182</v>
+        <v>612072905.47</v>
       </c>
       <c r="AV2" t="n">
-        <v>81457950.18000001</v>
+        <v>61561552.47</v>
       </c>
       <c r="AW2" t="n">
-        <v>2914678118.35</v>
+        <v>2265112553.39</v>
       </c>
       <c r="AX2" t="n">
-        <v>1097553475.04</v>
+        <v>793279487.98</v>
       </c>
       <c r="AY2" t="n">
-        <v>4012231593.39</v>
+        <v>3058392041.37</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4012231593.39</v>
+        <v>3058392041.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-5082738.214571</v>
+        <v>-5230970.072106</v>
       </c>
       <c r="C3" t="n">
-        <v>0.094945</v>
+        <v>0.111191</v>
       </c>
       <c r="D3" t="n">
-        <v>1058272533.99</v>
+        <v>1093466080.58</v>
       </c>
       <c r="E3" t="n">
-        <v>-53533424.81</v>
+        <v>-47044845.17</v>
       </c>
       <c r="F3" t="n">
-        <v>-53533424.81</v>
+        <v>-47044845.17</v>
       </c>
       <c r="G3" t="n">
-        <v>580066240.84</v>
+        <v>637091085.6</v>
       </c>
       <c r="H3" t="n">
-        <v>345605755.48</v>
+        <v>320157679.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1057551549.04</v>
+        <v>993612412.28</v>
       </c>
       <c r="J3" t="n">
-        <v>1004739109.18</v>
+        <v>1046421235.41</v>
       </c>
       <c r="K3" t="n">
-        <v>659133353.7</v>
+        <v>726263555.71</v>
       </c>
       <c r="L3" t="n">
-        <v>50774211.36</v>
+        <v>99861652.34999999</v>
       </c>
       <c r="M3" t="n">
-        <v>17372581.84</v>
+        <v>12538533.79</v>
       </c>
       <c r="N3" t="n">
-        <v>68644333.17</v>
+        <v>112800293.38</v>
       </c>
       <c r="O3" t="n">
-        <v>628516927.435429</v>
+        <v>678904960.697894</v>
       </c>
       <c r="P3" t="n">
-        <v>580066240.84</v>
+        <v>637091085.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2722087218.73</v>
+        <v>2849524927.57</v>
       </c>
       <c r="R3" t="n">
-        <v>655975988.28</v>
+        <v>727435986.77</v>
       </c>
       <c r="S3" t="n">
-        <v>1115512002</v>
+        <v>1098432906</v>
       </c>
       <c r="T3" t="n">
-        <v>1115512002</v>
+        <v>1098432906</v>
       </c>
       <c r="U3" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="V3" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="W3" t="n">
-        <v>580066240.84</v>
+        <v>637091085.6</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>580066240.84</v>
+        <v>637091085.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>-762468.27</v>
+        <v>2725964.13</v>
       </c>
       <c r="AA3" t="n">
-        <v>580828709.11</v>
+        <v>634365121.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>580828709.11</v>
+        <v>634365121.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>60932062.75</v>
+        <v>79359900.45</v>
       </c>
       <c r="AD3" t="n">
-        <v>641760771.86</v>
+        <v>713725021.92</v>
       </c>
       <c r="AE3" t="n">
-        <v>-14038039.65</v>
+        <v>-15584905.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>-61449119.64</v>
+        <v>-52730010.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>477669.8</v>
+        <v>182228</v>
       </c>
       <c r="AH3" t="n">
-        <v>2417268.64</v>
+        <v>-4175927.12</v>
       </c>
       <c r="AI3" t="n">
-        <v>58554181.2</v>
+        <v>56723709.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>50774211.36</v>
+        <v>99861652.34999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>497539.97</v>
+        <v>400107.24</v>
       </c>
       <c r="AL3" t="n">
-        <v>17372581.84</v>
+        <v>12538533.79</v>
       </c>
       <c r="AM3" t="n">
-        <v>68644333.17</v>
+        <v>112800293.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>643256124</v>
+        <v>632486450.53</v>
       </c>
       <c r="AO3" t="n">
-        <v>1664535669.69</v>
+        <v>1855912515.29</v>
       </c>
       <c r="AP3" t="n">
-        <v>43557507.29</v>
+        <v>46933597.71</v>
       </c>
       <c r="AQ3" t="n">
-        <v>36766344.43</v>
+        <v>43374031.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>36766344.43</v>
+        <v>43374031.05</v>
       </c>
       <c r="AS3" t="n">
-        <v>409194024.26</v>
+        <v>533749697.34</v>
       </c>
       <c r="AT3" t="n">
-        <v>709494304.64</v>
+        <v>798281832.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>606685750.75</v>
+        <v>735541649.42</v>
       </c>
       <c r="AV3" t="n">
-        <v>102808553.89</v>
+        <v>62740182.61</v>
       </c>
       <c r="AW3" t="n">
-        <v>2307791793.69</v>
+        <v>2488398965.82</v>
       </c>
       <c r="AX3" t="n">
-        <v>1057551549.04</v>
+        <v>993612412.28</v>
       </c>
       <c r="AY3" t="n">
-        <v>3365343342.73</v>
+        <v>3482011378.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3365343342.73</v>
+        <v>3482011378.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-5230970.072106</v>
+        <v>-5082738.214571</v>
       </c>
       <c r="C4" t="n">
-        <v>0.111191</v>
+        <v>0.094945</v>
       </c>
       <c r="D4" t="n">
-        <v>1093466080.58</v>
+        <v>1058272533.99</v>
       </c>
       <c r="E4" t="n">
-        <v>-47044845.17</v>
+        <v>-53533424.81</v>
       </c>
       <c r="F4" t="n">
-        <v>-47044845.17</v>
+        <v>-53533424.81</v>
       </c>
       <c r="G4" t="n">
-        <v>637091085.6</v>
+        <v>580066240.84</v>
       </c>
       <c r="H4" t="n">
-        <v>320157679.7</v>
+        <v>345605755.48</v>
       </c>
       <c r="I4" t="n">
-        <v>993612412.28</v>
+        <v>1057551549.04</v>
       </c>
       <c r="J4" t="n">
-        <v>1046421235.41</v>
+        <v>1004739109.18</v>
       </c>
       <c r="K4" t="n">
-        <v>726263555.71</v>
+        <v>659133353.7</v>
       </c>
       <c r="L4" t="n">
-        <v>99861652.34999999</v>
+        <v>50774211.36</v>
       </c>
       <c r="M4" t="n">
-        <v>12538533.79</v>
+        <v>17372581.84</v>
       </c>
       <c r="N4" t="n">
-        <v>112800293.38</v>
+        <v>68644333.17</v>
       </c>
       <c r="O4" t="n">
-        <v>678904960.697894</v>
+        <v>628516927.435429</v>
       </c>
       <c r="P4" t="n">
-        <v>637091085.6</v>
+        <v>580066240.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>2849524927.57</v>
+        <v>2722087218.73</v>
       </c>
       <c r="R4" t="n">
-        <v>727435986.77</v>
+        <v>655975988.28</v>
       </c>
       <c r="S4" t="n">
-        <v>1098432906</v>
+        <v>1115512002</v>
       </c>
       <c r="T4" t="n">
-        <v>1098432906</v>
+        <v>1115512002</v>
       </c>
       <c r="U4" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="V4" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="W4" t="n">
-        <v>637091085.6</v>
+        <v>580066240.84</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>637091085.6</v>
+        <v>580066240.84</v>
       </c>
       <c r="Z4" t="n">
-        <v>2725964.13</v>
+        <v>-762468.27</v>
       </c>
       <c r="AA4" t="n">
-        <v>634365121.47</v>
+        <v>580828709.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>634365121.47</v>
+        <v>580828709.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>79359900.45</v>
+        <v>60932062.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>713725021.92</v>
+        <v>641760771.86</v>
       </c>
       <c r="AE4" t="n">
-        <v>-15584905.33</v>
+        <v>-14038039.65</v>
       </c>
       <c r="AF4" t="n">
-        <v>-52730010.08</v>
+        <v>-61449119.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>182228</v>
+        <v>477669.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>-4175927.12</v>
+        <v>2417268.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>56723709.2</v>
+        <v>58554181.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99861652.34999999</v>
+        <v>50774211.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>400107.24</v>
+        <v>497539.97</v>
       </c>
       <c r="AL4" t="n">
-        <v>12538533.79</v>
+        <v>17372581.84</v>
       </c>
       <c r="AM4" t="n">
-        <v>112800293.38</v>
+        <v>68644333.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>632486450.53</v>
+        <v>643256124</v>
       </c>
       <c r="AO4" t="n">
-        <v>1855912515.29</v>
+        <v>1664535669.69</v>
       </c>
       <c r="AP4" t="n">
-        <v>46933597.71</v>
+        <v>43557507.29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>43374031.05</v>
+        <v>36766344.43</v>
       </c>
       <c r="AR4" t="n">
-        <v>43374031.05</v>
+        <v>36766344.43</v>
       </c>
       <c r="AS4" t="n">
-        <v>533749697.34</v>
+        <v>409194024.26</v>
       </c>
       <c r="AT4" t="n">
-        <v>798281832.03</v>
+        <v>709494304.64</v>
       </c>
       <c r="AU4" t="n">
-        <v>735541649.42</v>
+        <v>606685750.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>62740182.61</v>
+        <v>102808553.89</v>
       </c>
       <c r="AW4" t="n">
-        <v>2488398965.82</v>
+        <v>2307791793.69</v>
       </c>
       <c r="AX4" t="n">
-        <v>993612412.28</v>
+        <v>1057551549.04</v>
       </c>
       <c r="AY4" t="n">
-        <v>3482011378.1</v>
+        <v>3365343342.73</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3482011378.1</v>
+        <v>3365343342.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-18621903.553366</v>
+        <v>-8221788.181347</v>
       </c>
       <c r="C5" t="n">
-        <v>0.119232</v>
+        <v>0.043257</v>
       </c>
       <c r="D5" t="n">
-        <v>1070819320.53</v>
+        <v>1214991466.4</v>
       </c>
       <c r="E5" t="n">
-        <v>-156182639.1</v>
+        <v>-190069745.95</v>
       </c>
       <c r="F5" t="n">
-        <v>-156182639.1</v>
+        <v>-190069745.95</v>
       </c>
       <c r="G5" t="n">
-        <v>533726576.95</v>
+        <v>601569140.2</v>
       </c>
       <c r="H5" t="n">
-        <v>304268219.64</v>
+        <v>376231728.48</v>
       </c>
       <c r="I5" t="n">
-        <v>793279487.98</v>
+        <v>1097553475.04</v>
       </c>
       <c r="J5" t="n">
-        <v>914636681.4299999</v>
+        <v>1024921720.45</v>
       </c>
       <c r="K5" t="n">
-        <v>610368461.79</v>
+        <v>648689991.97</v>
       </c>
       <c r="L5" t="n">
-        <v>36778357.6</v>
+        <v>30475527.21</v>
       </c>
       <c r="M5" t="n">
-        <v>10526880.76</v>
+        <v>16173784.9</v>
       </c>
       <c r="N5" t="n">
-        <v>47658560.86</v>
+        <v>47064122.34</v>
       </c>
       <c r="O5" t="n">
-        <v>671287312.496634</v>
+        <v>783417097.968653</v>
       </c>
       <c r="P5" t="n">
-        <v>533726576.95</v>
+        <v>601569140.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2481247767.46</v>
+        <v>3241039750.43</v>
       </c>
       <c r="R5" t="n">
-        <v>586195029.24</v>
+        <v>646309880.85</v>
       </c>
       <c r="S5" t="n">
-        <v>1067453154</v>
+        <v>1114016926</v>
       </c>
       <c r="T5" t="n">
-        <v>1067453154</v>
+        <v>1114016926</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="W5" t="n">
-        <v>533726576.95</v>
+        <v>601569140.2</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>533726576.95</v>
+        <v>601569140.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>5405058.16</v>
+        <v>-3586509.04</v>
       </c>
       <c r="AA5" t="n">
-        <v>528321518.79</v>
+        <v>605155649.24</v>
       </c>
       <c r="AB5" t="n">
-        <v>528321518.79</v>
+        <v>605155649.24</v>
       </c>
       <c r="AC5" t="n">
-        <v>71520062.23999999</v>
+        <v>27360557.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>599841581.03</v>
+        <v>632516207.0700001</v>
       </c>
       <c r="AE5" t="n">
-        <v>13646551.79</v>
+        <v>-13793673.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>-156182639.1</v>
+        <v>-204582703.96</v>
       </c>
       <c r="AG5" t="n">
-        <v>1296526.19</v>
+        <v>148625.82</v>
       </c>
       <c r="AH5" t="n">
-        <v>7623146.39</v>
+        <v>6442945</v>
       </c>
       <c r="AI5" t="n">
-        <v>147262966.52</v>
+        <v>197991133.14</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36778357.6</v>
+        <v>30475527.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>353322.5</v>
+        <v>414810.23</v>
       </c>
       <c r="AL5" t="n">
-        <v>10526880.76</v>
+        <v>16173784.9</v>
       </c>
       <c r="AM5" t="n">
-        <v>47658560.86</v>
+        <v>47064122.34</v>
       </c>
       <c r="AN5" t="n">
-        <v>577144273.91</v>
+        <v>771191842.96</v>
       </c>
       <c r="AO5" t="n">
-        <v>1687968279.48</v>
+        <v>2143486275.39</v>
       </c>
       <c r="AP5" t="n">
-        <v>44978643.62</v>
+        <v>50865074.41</v>
       </c>
       <c r="AQ5" t="n">
-        <v>134235745.19</v>
+        <v>33763392.05</v>
       </c>
       <c r="AR5" t="n">
-        <v>134235745.19</v>
+        <v>33763392.05</v>
       </c>
       <c r="AS5" t="n">
-        <v>357368428.49</v>
+        <v>421239678.51</v>
       </c>
       <c r="AT5" t="n">
-        <v>673634457.9400001</v>
+        <v>1061874132.18</v>
       </c>
       <c r="AU5" t="n">
-        <v>612072905.47</v>
+        <v>980416182</v>
       </c>
       <c r="AV5" t="n">
-        <v>61561552.47</v>
+        <v>81457950.18000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>2265112553.39</v>
+        <v>2914678118.35</v>
       </c>
       <c r="AX5" t="n">
-        <v>793279487.98</v>
+        <v>1097553475.04</v>
       </c>
       <c r="AY5" t="n">
-        <v>3058392041.37</v>
+        <v>4012231593.39</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3058392041.37</v>
+        <v>4012231593.39</v>
       </c>
     </row>
   </sheetData>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>1114816535</v>
@@ -1704,44 +1704,46 @@
         <v>1114816535</v>
       </c>
       <c r="D2" t="n">
-        <v>133878646.23</v>
+        <v>79097217.65000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5886406487.16</v>
+        <v>5935578917.64</v>
       </c>
       <c r="F2" t="n">
-        <v>8832145683.76</v>
+        <v>8096732516.95</v>
       </c>
       <c r="G2" t="n">
-        <v>2911644249.25</v>
+        <v>3390992207.94</v>
       </c>
       <c r="H2" t="n">
-        <v>5886406487.16</v>
+        <v>5935578917.64</v>
       </c>
       <c r="I2" t="n">
-        <v>4175081.31</v>
+        <v>9112598.939999999</v>
       </c>
       <c r="J2" t="n">
-        <v>8712145683.76</v>
+        <v>8033733976.67</v>
       </c>
       <c r="K2" t="n">
-        <v>8712145683.76</v>
+        <v>8033733976.67</v>
       </c>
       <c r="L2" t="n">
-        <v>8752316355.52</v>
+        <v>8045644445.25</v>
       </c>
       <c r="M2" t="n">
-        <v>40170671.76</v>
+        <v>11910468.58</v>
       </c>
       <c r="N2" t="n">
-        <v>8712145683.76</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>8033733976.67</v>
+      </c>
+      <c r="O2" t="n">
+        <v>327859278.84</v>
+      </c>
       <c r="P2" t="n">
-        <v>5093317008.69</v>
+        <v>4803513304.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1835052820.79</v>
+        <v>1930312175.73</v>
       </c>
       <c r="R2" t="n">
         <v>1114816535</v>
@@ -1750,170 +1752,170 @@
         <v>1114816535</v>
       </c>
       <c r="T2" t="n">
-        <v>1713287268.66</v>
+        <v>1198240568.74</v>
       </c>
       <c r="U2" t="n">
-        <v>600319940.41</v>
+        <v>185400027.67</v>
       </c>
       <c r="V2" t="n">
-        <v>433135504.83</v>
+        <v>82573151.65000001</v>
       </c>
       <c r="W2" t="n">
-        <v>142037566.58</v>
-      </c>
-      <c r="X2" t="n">
-        <v>20971787.69</v>
-      </c>
+        <v>93714277.08</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>4175081.31</v>
+        <v>9112598.939999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>4175081.31</v>
+        <v>9112598.939999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>1112967328.25</v>
+        <v>1012840541.07</v>
       </c>
       <c r="AB2" t="n">
-        <v>13498895.6</v>
+        <v>5350624.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>129703564.92</v>
+        <v>69984618.70999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>120000000</v>
+        <v>62998540.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>931544927.5599999</v>
+        <v>839519011.71</v>
       </c>
       <c r="AF2" t="n">
-        <v>765986485.16</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>588316019.3099999</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>551116.8</v>
+      </c>
       <c r="AH2" t="n">
-        <v>39464329.51</v>
+        <v>62979732.61</v>
       </c>
       <c r="AI2" t="n">
-        <v>126094112.89</v>
+        <v>187672142.99</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10465603624.18</v>
+        <v>9243885013.99</v>
       </c>
       <c r="AK2" t="n">
-        <v>6440992046.68</v>
+        <v>4840052264.98</v>
       </c>
       <c r="AL2" t="n">
-        <v>680892670.96</v>
+        <v>207136733.14</v>
       </c>
       <c r="AM2" t="n">
-        <v>117185901.75</v>
+        <v>84579673.01000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>151241887.88</v>
+        <v>82012896.14</v>
       </c>
       <c r="AO2" t="n">
-        <v>916185438.0599999</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>303334298.25</v>
-      </c>
+        <v>423118722.55</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>612851139.8099999</v>
+        <v>423118722.55</v>
       </c>
       <c r="AR2" t="n">
-        <v>289685398.69</v>
+        <v>278703502.76</v>
       </c>
       <c r="AS2" t="n">
-        <v>30102306.66</v>
+        <v>28613781.25</v>
       </c>
       <c r="AT2" t="n">
-        <v>2825739196.6</v>
+        <v>2098155059.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>2814826733.1</v>
+        <v>2011017285.99</v>
       </c>
       <c r="AV2" t="n">
-        <v>10912463.5</v>
+        <v>87137773.04000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>1429959246.08</v>
+        <v>1637731897.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>-1132083486.66</v>
+        <v>-807954775.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>2562042732.74</v>
+        <v>2445686672.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>62331740.66</v>
+        <v>94128642.40000001</v>
       </c>
       <c r="BA2" t="n">
-        <v>323426798.49</v>
+        <v>234350867.46</v>
       </c>
       <c r="BB2" t="n">
-        <v>954261732.54</v>
+        <v>898958219.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1222022461.05</v>
+        <v>1218248942.94</v>
       </c>
       <c r="BD2" t="n">
-        <v>4024611577.5</v>
+        <v>4403832749.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1008622657.65</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>33016115.27</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>11733281.17</v>
+      </c>
       <c r="BG2" t="n">
-        <v>60248046.96</v>
+        <v>13246983.07</v>
       </c>
       <c r="BH2" t="n">
-        <v>506755690.8</v>
+        <v>420454524.37</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11896804.14</v>
+        <v>20242150.98</v>
       </c>
       <c r="BK2" t="n">
-        <v>203265480.86</v>
+        <v>146428715.7</v>
       </c>
       <c r="BL2" t="n">
-        <v>182326555.55</v>
+        <v>126219608.33</v>
       </c>
       <c r="BM2" t="n">
-        <v>109266850.25</v>
+        <v>127564049.36</v>
       </c>
       <c r="BN2" t="n">
-        <v>72964936.67</v>
+        <v>233937339.75</v>
       </c>
       <c r="BO2" t="n">
-        <v>516751549.66</v>
+        <v>395573728.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>-24926436.14</v>
+        <v>-14043258.66</v>
       </c>
       <c r="BQ2" t="n">
-        <v>541677985.8</v>
+        <v>409616987.46</v>
       </c>
       <c r="BR2" t="n">
-        <v>1859268695.76</v>
+        <v>3295870776.58</v>
       </c>
       <c r="BS2" t="n">
-        <v>733857973.63</v>
+        <v>60000000</v>
       </c>
       <c r="BT2" t="n">
-        <v>1125410722.13</v>
+        <v>3235870776.58</v>
       </c>
       <c r="BU2" t="n">
-        <v>3552229.93</v>
+        <v>22172189.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>1104655208.72</v>
+        <v>3213698587.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1114816535</v>
@@ -1922,46 +1924,46 @@
         <v>1114816535</v>
       </c>
       <c r="D3" t="n">
-        <v>63465860.45</v>
+        <v>208233292.4</v>
       </c>
       <c r="E3" t="n">
-        <v>5392302136.16</v>
+        <v>5695818382.54</v>
       </c>
       <c r="F3" t="n">
-        <v>8058993837.21</v>
+        <v>8118067905.38</v>
       </c>
       <c r="G3" t="n">
-        <v>2498137923.55</v>
+        <v>3107779931.64</v>
       </c>
       <c r="H3" t="n">
-        <v>5392302136.16</v>
+        <v>5695818382.54</v>
       </c>
       <c r="I3" t="n">
-        <v>12538653.69</v>
+        <v>19582568.73</v>
       </c>
       <c r="J3" t="n">
-        <v>8018993837.21</v>
+        <v>7940881639.27</v>
       </c>
       <c r="K3" t="n">
-        <v>8018993837.21</v>
+        <v>7940881639.27</v>
       </c>
       <c r="L3" t="n">
-        <v>8055426359.75</v>
+        <v>7976693331.52</v>
       </c>
       <c r="M3" t="n">
-        <v>36432522.54</v>
+        <v>35811692.25</v>
       </c>
       <c r="N3" t="n">
-        <v>8018993837.21</v>
+        <v>7940881639.27</v>
       </c>
       <c r="O3" t="n">
         <v>602164494.8</v>
       </c>
       <c r="P3" t="n">
-        <v>5037427374.49</v>
+        <v>5003040639.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>1834181195.27</v>
+        <v>1834129346.39</v>
       </c>
       <c r="R3" t="n">
         <v>1114816535</v>
@@ -1970,168 +1972,172 @@
         <v>1114816535</v>
       </c>
       <c r="T3" t="n">
-        <v>1341246394.27</v>
+        <v>1778575769.91</v>
       </c>
       <c r="U3" t="n">
-        <v>526162394.15</v>
+        <v>174939940.92</v>
       </c>
       <c r="V3" t="n">
-        <v>416473652.88</v>
+        <v>29641248.86</v>
       </c>
       <c r="W3" t="n">
-        <v>84114120.79000001</v>
+        <v>98534696</v>
       </c>
       <c r="X3" t="n">
-        <v>13035966.79</v>
+        <v>27181427.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>12538653.69</v>
+        <v>19582568.73</v>
       </c>
       <c r="Z3" t="n">
-        <v>12538653.69</v>
+        <v>19582568.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>815084000.12</v>
+        <v>1603635828.99</v>
       </c>
       <c r="AB3" t="n">
-        <v>35686430.73</v>
+        <v>426815699.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>50927206.76</v>
+        <v>188650723.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>40000000</v>
+        <v>177186266.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>699056850.87</v>
+        <v>943630754.41</v>
       </c>
       <c r="AF3" t="n">
-        <v>503406791.36</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>654452729.51</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>653000.61</v>
+      </c>
       <c r="AH3" t="n">
-        <v>39643159.43</v>
+        <v>68878034.51000001</v>
       </c>
       <c r="AI3" t="n">
-        <v>156006900.08</v>
+        <v>219646989.78</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9396672754.02</v>
+        <v>9755269101.43</v>
       </c>
       <c r="AK3" t="n">
-        <v>6083450830.35</v>
+        <v>5043853340.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>959681370.52</v>
+        <v>320832456.34</v>
       </c>
       <c r="AM3" t="n">
-        <v>117984776.08</v>
+        <v>124754542.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>87401411.89</v>
+        <v>88420909.83</v>
       </c>
       <c r="AO3" t="n">
-        <v>511179553.91</v>
+        <v>426417754.51</v>
       </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>511179553.91</v>
+        <v>426417754.51</v>
       </c>
       <c r="AR3" t="n">
-        <v>290738967</v>
+        <v>297728370.49</v>
       </c>
       <c r="AS3" t="n">
-        <v>32345137.09</v>
+        <v>34732624.44</v>
       </c>
       <c r="AT3" t="n">
-        <v>2626691701.05</v>
+        <v>2245063256.73</v>
       </c>
       <c r="AU3" t="n">
-        <v>2615779237.55</v>
+        <v>2184536050.14</v>
       </c>
       <c r="AV3" t="n">
-        <v>10912463.5</v>
+        <v>60527206.59</v>
       </c>
       <c r="AW3" t="n">
-        <v>1457427912.81</v>
+        <v>1505903426.17</v>
       </c>
       <c r="AX3" t="n">
-        <v>-1023144433.91</v>
+        <v>-911676616.67</v>
       </c>
       <c r="AY3" t="n">
-        <v>2480572346.72</v>
+        <v>2417580042.84</v>
       </c>
       <c r="AZ3" t="n">
-        <v>34354210.39</v>
+        <v>37595192.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>288058299.86</v>
+        <v>268151229.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>940556880.4299999</v>
+        <v>904161297.63</v>
       </c>
       <c r="BC3" t="n">
-        <v>1217602956.04</v>
+        <v>1207672323.41</v>
       </c>
       <c r="BD3" t="n">
-        <v>3313221923.67</v>
+        <v>4711415760.63</v>
       </c>
       <c r="BE3" t="n">
-        <v>721815519.96</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>542070558.3200001</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>11733281.17</v>
+      </c>
       <c r="BG3" t="n">
-        <v>26125128.56</v>
+        <v>34130968.41</v>
       </c>
       <c r="BH3" t="n">
-        <v>490857450.66</v>
+        <v>543534405.1900001</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12928533.91</v>
+        <v>12278999.26</v>
       </c>
       <c r="BK3" t="n">
-        <v>208532049.39</v>
+        <v>246015462.3</v>
       </c>
       <c r="BL3" t="n">
-        <v>139045259.3</v>
+        <v>153594186.63</v>
       </c>
       <c r="BM3" t="n">
-        <v>130351608.06</v>
+        <v>131645757</v>
       </c>
       <c r="BN3" t="n">
-        <v>98990097.89</v>
+        <v>81147149.20999999</v>
       </c>
       <c r="BO3" t="n">
-        <v>467398830.97</v>
+        <v>499970782.39</v>
       </c>
       <c r="BP3" t="n">
-        <v>-19422710.15</v>
+        <v>-16991381.28</v>
       </c>
       <c r="BQ3" t="n">
-        <v>486821541.12</v>
+        <v>516962163.67</v>
       </c>
       <c r="BR3" t="n">
-        <v>1508034895.63</v>
+        <v>2998828615.94</v>
       </c>
       <c r="BS3" t="n">
-        <v>186059832.88</v>
+        <v>328361918.37</v>
       </c>
       <c r="BT3" t="n">
-        <v>1321975062.75</v>
+        <v>2670466697.57</v>
       </c>
       <c r="BU3" t="n">
-        <v>1957322.94</v>
+        <v>91163495.77</v>
       </c>
       <c r="BV3" t="n">
-        <v>2222874.8</v>
+        <v>2550627768.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1114816535</v>
@@ -2140,46 +2146,46 @@
         <v>1114816535</v>
       </c>
       <c r="D4" t="n">
-        <v>208233292.4</v>
+        <v>63465860.45</v>
       </c>
       <c r="E4" t="n">
-        <v>5695818382.54</v>
+        <v>5392302136.16</v>
       </c>
       <c r="F4" t="n">
-        <v>8118067905.38</v>
+        <v>8058993837.21</v>
       </c>
       <c r="G4" t="n">
-        <v>3107779931.64</v>
+        <v>2498137923.55</v>
       </c>
       <c r="H4" t="n">
-        <v>5695818382.54</v>
+        <v>5392302136.16</v>
       </c>
       <c r="I4" t="n">
-        <v>19582568.73</v>
+        <v>12538653.69</v>
       </c>
       <c r="J4" t="n">
-        <v>7940881639.27</v>
+        <v>8018993837.21</v>
       </c>
       <c r="K4" t="n">
-        <v>7940881639.27</v>
+        <v>8018993837.21</v>
       </c>
       <c r="L4" t="n">
-        <v>7976693331.52</v>
+        <v>8055426359.75</v>
       </c>
       <c r="M4" t="n">
-        <v>35811692.25</v>
+        <v>36432522.54</v>
       </c>
       <c r="N4" t="n">
-        <v>7940881639.27</v>
+        <v>8018993837.21</v>
       </c>
       <c r="O4" t="n">
         <v>602164494.8</v>
       </c>
       <c r="P4" t="n">
-        <v>5003040639.65</v>
+        <v>5037427374.49</v>
       </c>
       <c r="Q4" t="n">
-        <v>1834129346.39</v>
+        <v>1834181195.27</v>
       </c>
       <c r="R4" t="n">
         <v>1114816535</v>
@@ -2188,172 +2194,168 @@
         <v>1114816535</v>
       </c>
       <c r="T4" t="n">
-        <v>1778575769.91</v>
+        <v>1341246394.27</v>
       </c>
       <c r="U4" t="n">
-        <v>174939940.92</v>
+        <v>526162394.15</v>
       </c>
       <c r="V4" t="n">
-        <v>29641248.86</v>
+        <v>416473652.88</v>
       </c>
       <c r="W4" t="n">
-        <v>98534696</v>
+        <v>84114120.79000001</v>
       </c>
       <c r="X4" t="n">
-        <v>27181427.33</v>
+        <v>13035966.79</v>
       </c>
       <c r="Y4" t="n">
-        <v>19582568.73</v>
+        <v>12538653.69</v>
       </c>
       <c r="Z4" t="n">
-        <v>19582568.73</v>
+        <v>12538653.69</v>
       </c>
       <c r="AA4" t="n">
-        <v>1603635828.99</v>
+        <v>815084000.12</v>
       </c>
       <c r="AB4" t="n">
-        <v>426815699.65</v>
+        <v>35686430.73</v>
       </c>
       <c r="AC4" t="n">
-        <v>188650723.67</v>
+        <v>50927206.76</v>
       </c>
       <c r="AD4" t="n">
-        <v>177186266.11</v>
+        <v>40000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>943630754.41</v>
+        <v>699056850.87</v>
       </c>
       <c r="AF4" t="n">
-        <v>654452729.51</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>653000.61</v>
-      </c>
+        <v>503406791.36</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>68878034.51000001</v>
+        <v>39643159.43</v>
       </c>
       <c r="AI4" t="n">
-        <v>219646989.78</v>
+        <v>156006900.08</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9755269101.43</v>
+        <v>9396672754.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>5043853340.8</v>
+        <v>6083450830.35</v>
       </c>
       <c r="AL4" t="n">
-        <v>320832456.34</v>
+        <v>959681370.52</v>
       </c>
       <c r="AM4" t="n">
-        <v>124754542.29</v>
+        <v>117984776.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>88420909.83</v>
+        <v>87401411.89</v>
       </c>
       <c r="AO4" t="n">
-        <v>426417754.51</v>
+        <v>511179553.91</v>
       </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>426417754.51</v>
+        <v>511179553.91</v>
       </c>
       <c r="AR4" t="n">
-        <v>297728370.49</v>
+        <v>290738967</v>
       </c>
       <c r="AS4" t="n">
-        <v>34732624.44</v>
+        <v>32345137.09</v>
       </c>
       <c r="AT4" t="n">
-        <v>2245063256.73</v>
+        <v>2626691701.05</v>
       </c>
       <c r="AU4" t="n">
-        <v>2184536050.14</v>
+        <v>2615779237.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>60527206.59</v>
+        <v>10912463.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1505903426.17</v>
+        <v>1457427912.81</v>
       </c>
       <c r="AX4" t="n">
-        <v>-911676616.67</v>
+        <v>-1023144433.91</v>
       </c>
       <c r="AY4" t="n">
-        <v>2417580042.84</v>
+        <v>2480572346.72</v>
       </c>
       <c r="AZ4" t="n">
-        <v>37595192.4</v>
+        <v>34354210.39</v>
       </c>
       <c r="BA4" t="n">
-        <v>268151229.4</v>
+        <v>288058299.86</v>
       </c>
       <c r="BB4" t="n">
-        <v>904161297.63</v>
+        <v>940556880.4299999</v>
       </c>
       <c r="BC4" t="n">
-        <v>1207672323.41</v>
+        <v>1217602956.04</v>
       </c>
       <c r="BD4" t="n">
-        <v>4711415760.63</v>
+        <v>3313221923.67</v>
       </c>
       <c r="BE4" t="n">
-        <v>542070558.3200001</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>11733281.17</v>
-      </c>
+        <v>721815519.96</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>34130968.41</v>
+        <v>26125128.56</v>
       </c>
       <c r="BH4" t="n">
-        <v>543534405.1900001</v>
+        <v>490857450.66</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12278999.26</v>
+        <v>12928533.91</v>
       </c>
       <c r="BK4" t="n">
-        <v>246015462.3</v>
+        <v>208532049.39</v>
       </c>
       <c r="BL4" t="n">
-        <v>153594186.63</v>
+        <v>139045259.3</v>
       </c>
       <c r="BM4" t="n">
-        <v>131645757</v>
+        <v>130351608.06</v>
       </c>
       <c r="BN4" t="n">
-        <v>81147149.20999999</v>
+        <v>98990097.89</v>
       </c>
       <c r="BO4" t="n">
-        <v>499970782.39</v>
+        <v>467398830.97</v>
       </c>
       <c r="BP4" t="n">
-        <v>-16991381.28</v>
+        <v>-19422710.15</v>
       </c>
       <c r="BQ4" t="n">
-        <v>516962163.67</v>
+        <v>486821541.12</v>
       </c>
       <c r="BR4" t="n">
-        <v>2998828615.94</v>
+        <v>1508034895.63</v>
       </c>
       <c r="BS4" t="n">
-        <v>328361918.37</v>
+        <v>186059832.88</v>
       </c>
       <c r="BT4" t="n">
-        <v>2670466697.57</v>
+        <v>1321975062.75</v>
       </c>
       <c r="BU4" t="n">
-        <v>91163495.77</v>
+        <v>1957322.94</v>
       </c>
       <c r="BV4" t="n">
-        <v>2550627768.31</v>
+        <v>2222874.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1114816535</v>
@@ -2362,46 +2364,44 @@
         <v>1114816535</v>
       </c>
       <c r="D5" t="n">
-        <v>79097217.65000001</v>
+        <v>133878646.23</v>
       </c>
       <c r="E5" t="n">
-        <v>5935578917.64</v>
+        <v>5886406487.16</v>
       </c>
       <c r="F5" t="n">
-        <v>8096732516.95</v>
+        <v>8832145683.76</v>
       </c>
       <c r="G5" t="n">
-        <v>3390992207.94</v>
+        <v>2911644249.25</v>
       </c>
       <c r="H5" t="n">
-        <v>5935578917.64</v>
+        <v>5886406487.16</v>
       </c>
       <c r="I5" t="n">
-        <v>9112598.939999999</v>
+        <v>4175081.31</v>
       </c>
       <c r="J5" t="n">
-        <v>8033733976.67</v>
+        <v>8712145683.76</v>
       </c>
       <c r="K5" t="n">
-        <v>8033733976.67</v>
+        <v>8712145683.76</v>
       </c>
       <c r="L5" t="n">
-        <v>8045644445.25</v>
+        <v>8752316355.52</v>
       </c>
       <c r="M5" t="n">
-        <v>11910468.58</v>
+        <v>40170671.76</v>
       </c>
       <c r="N5" t="n">
-        <v>8033733976.67</v>
-      </c>
-      <c r="O5" t="n">
-        <v>327859278.84</v>
-      </c>
+        <v>8712145683.76</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>4803513304.16</v>
+        <v>5093317008.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>1930312175.73</v>
+        <v>1835052820.79</v>
       </c>
       <c r="R5" t="n">
         <v>1114816535</v>
@@ -2410,165 +2410,165 @@
         <v>1114816535</v>
       </c>
       <c r="T5" t="n">
-        <v>1198240568.74</v>
+        <v>1713287268.66</v>
       </c>
       <c r="U5" t="n">
-        <v>185400027.67</v>
+        <v>600319940.41</v>
       </c>
       <c r="V5" t="n">
-        <v>82573151.65000001</v>
+        <v>433135504.83</v>
       </c>
       <c r="W5" t="n">
-        <v>93714277.08</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>142037566.58</v>
+      </c>
+      <c r="X5" t="n">
+        <v>20971787.69</v>
+      </c>
       <c r="Y5" t="n">
-        <v>9112598.939999999</v>
+        <v>4175081.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>9112598.939999999</v>
+        <v>4175081.31</v>
       </c>
       <c r="AA5" t="n">
-        <v>1012840541.07</v>
+        <v>1112967328.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>5350624.29</v>
+        <v>13498895.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>69984618.70999999</v>
+        <v>129703564.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>62998540.28</v>
+        <v>120000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>839519011.71</v>
+        <v>931544927.5599999</v>
       </c>
       <c r="AF5" t="n">
-        <v>588316019.3099999</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>551116.8</v>
-      </c>
+        <v>765986485.16</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>62979732.61</v>
+        <v>39464329.51</v>
       </c>
       <c r="AI5" t="n">
-        <v>187672142.99</v>
+        <v>126094112.89</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9243885013.99</v>
+        <v>10465603624.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>4840052264.98</v>
+        <v>6440992046.68</v>
       </c>
       <c r="AL5" t="n">
-        <v>207136733.14</v>
+        <v>680892670.96</v>
       </c>
       <c r="AM5" t="n">
-        <v>84579673.01000001</v>
+        <v>117185901.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>82012896.14</v>
+        <v>151241887.88</v>
       </c>
       <c r="AO5" t="n">
-        <v>423118722.55</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>916185438.0599999</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>303334298.25</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>423118722.55</v>
+        <v>612851139.8099999</v>
       </c>
       <c r="AR5" t="n">
-        <v>278703502.76</v>
+        <v>289685398.69</v>
       </c>
       <c r="AS5" t="n">
-        <v>28613781.25</v>
+        <v>30102306.66</v>
       </c>
       <c r="AT5" t="n">
-        <v>2098155059.03</v>
+        <v>2825739196.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>2011017285.99</v>
+        <v>2814826733.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>87137773.04000001</v>
+        <v>10912463.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1637731897.1</v>
+        <v>1429959246.08</v>
       </c>
       <c r="AX5" t="n">
-        <v>-807954775.1</v>
+        <v>-1132083486.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>2445686672.2</v>
+        <v>2562042732.74</v>
       </c>
       <c r="AZ5" t="n">
-        <v>94128642.40000001</v>
+        <v>62331740.66</v>
       </c>
       <c r="BA5" t="n">
-        <v>234350867.46</v>
+        <v>323426798.49</v>
       </c>
       <c r="BB5" t="n">
-        <v>898958219.4</v>
+        <v>954261732.54</v>
       </c>
       <c r="BC5" t="n">
-        <v>1218248942.94</v>
+        <v>1222022461.05</v>
       </c>
       <c r="BD5" t="n">
-        <v>4403832749.01</v>
+        <v>4024611577.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>33016115.27</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>11733281.17</v>
-      </c>
+        <v>1008622657.65</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>13246983.07</v>
+        <v>60248046.96</v>
       </c>
       <c r="BH5" t="n">
-        <v>420454524.37</v>
+        <v>506755690.8</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>20242150.98</v>
+        <v>11896804.14</v>
       </c>
       <c r="BK5" t="n">
-        <v>146428715.7</v>
+        <v>203265480.86</v>
       </c>
       <c r="BL5" t="n">
-        <v>126219608.33</v>
+        <v>182326555.55</v>
       </c>
       <c r="BM5" t="n">
-        <v>127564049.36</v>
+        <v>109266850.25</v>
       </c>
       <c r="BN5" t="n">
-        <v>233937339.75</v>
+        <v>72964936.67</v>
       </c>
       <c r="BO5" t="n">
-        <v>395573728.8</v>
+        <v>516751549.66</v>
       </c>
       <c r="BP5" t="n">
-        <v>-14043258.66</v>
+        <v>-24926436.14</v>
       </c>
       <c r="BQ5" t="n">
-        <v>409616987.46</v>
+        <v>541677985.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>3295870776.58</v>
+        <v>1859268695.76</v>
       </c>
       <c r="BS5" t="n">
-        <v>60000000</v>
+        <v>733857973.63</v>
       </c>
       <c r="BT5" t="n">
-        <v>3235870776.58</v>
+        <v>1125410722.13</v>
       </c>
       <c r="BU5" t="n">
-        <v>22172189.33</v>
+        <v>3552229.93</v>
       </c>
       <c r="BV5" t="n">
-        <v>3213698587.25</v>
+        <v>1104655208.72</v>
       </c>
     </row>
   </sheetData>
@@ -2809,550 +2809,550 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>561445148.23</v>
+        <v>702477754.28</v>
       </c>
       <c r="C2" t="n">
-        <v>-39838124.98</v>
+        <v>-639517504</v>
       </c>
       <c r="D2" t="n">
-        <v>119296750.01</v>
+        <v>303900000</v>
       </c>
       <c r="E2" t="n">
-        <v>-624813272.52</v>
+        <v>-482500771.37</v>
       </c>
       <c r="F2" t="n">
-        <v>1104655208.72</v>
+        <v>3222018234.91</v>
       </c>
       <c r="G2" t="n">
-        <v>1318160573.6</v>
+        <v>865134656.27</v>
       </c>
       <c r="H2" t="n">
-        <v>3947050.81</v>
+        <v>-6774739.78</v>
       </c>
       <c r="I2" t="n">
-        <v>-217452415.69</v>
+        <v>2363658318.42</v>
       </c>
       <c r="J2" t="n">
-        <v>121841261.13</v>
+        <v>1548327729.35</v>
       </c>
       <c r="K2" t="n">
-        <v>588417878.22</v>
+        <v>1900389917.95</v>
       </c>
       <c r="L2" t="n">
-        <v>-546035242.12</v>
+        <v>-15543344.67</v>
       </c>
       <c r="M2" t="n">
-        <v>79458625.03</v>
+        <v>-335617504</v>
       </c>
       <c r="N2" t="n">
-        <v>79458625.03</v>
+        <v>-335617504</v>
       </c>
       <c r="O2" t="n">
-        <v>-39838124.98</v>
+        <v>-639517504</v>
       </c>
       <c r="P2" t="n">
-        <v>119296750.01</v>
+        <v>303900000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1525552097.57</v>
+        <v>-369647936.58</v>
       </c>
       <c r="R2" t="n">
-        <v>-901381028.14</v>
+        <v>111260230.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2458983104.06</v>
+        <v>609339253.7</v>
       </c>
       <c r="T2" t="n">
-        <v>-3360364132.2</v>
+        <v>-498079023</v>
       </c>
       <c r="U2" t="n">
-        <v>-624171069.4299999</v>
+        <v>-480908167.28</v>
       </c>
       <c r="V2" t="n">
-        <v>642203.09</v>
+        <v>1592604.09</v>
       </c>
       <c r="W2" t="n">
-        <v>-624813272.52</v>
+        <v>-482500771.37</v>
       </c>
       <c r="X2" t="n">
-        <v>1186258420.75</v>
+        <v>1184978525.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>8617876.300000001</v>
+        <v>297411490.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>-55904655.09</v>
+        <v>-3571070.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>178499956.42</v>
+        <v>277538888.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>-56401484.53</v>
+        <v>-46530969.49</v>
       </c>
       <c r="AC2" t="n">
-        <v>-57575940.5</v>
+        <v>69974642.13</v>
       </c>
       <c r="AD2" t="n">
-        <v>14664087.17</v>
+        <v>30682385.85</v>
       </c>
       <c r="AE2" t="n">
-        <v>376231728.48</v>
+        <v>304268219.64</v>
       </c>
       <c r="AF2" t="n">
-        <v>242130104.88</v>
+        <v>173484287.18</v>
       </c>
       <c r="AG2" t="n">
-        <v>134101623.6</v>
+        <v>130783932.46</v>
       </c>
       <c r="AH2" t="n">
-        <v>-47950017.61</v>
+        <v>-134237582.59</v>
       </c>
       <c r="AI2" t="n">
-        <v>2301927.42</v>
+        <v>3646380.16</v>
       </c>
       <c r="AJ2" t="n">
-        <v>605155649.24</v>
+        <v>528321518.79</v>
       </c>
       <c r="AK2" t="n">
-        <v>1186258420.75</v>
+        <v>1184978525.65</v>
       </c>
       <c r="AL2" t="n">
-        <v>-455262933.57</v>
+        <v>-324111772.31</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2678727351.29</v>
+        <v>-1924645359.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1114619849.24</v>
+        <v>-689931181.13</v>
       </c>
       <c r="AO2" t="n">
-        <v>-962503788.6900001</v>
+        <v>-740661494.34</v>
       </c>
       <c r="AP2" t="n">
-        <v>-601603713.36</v>
+        <v>-494052683.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4320248705.61</v>
+        <v>3433735657.13</v>
       </c>
       <c r="AR2" t="n">
-        <v>178101687.22</v>
+        <v>153664993.64</v>
       </c>
       <c r="AS2" t="n">
-        <v>4142147018.39</v>
+        <v>3280070663.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>168443417.75</v>
+        <v>371844616.82</v>
       </c>
       <c r="C3" t="n">
-        <v>-358626633.35</v>
+        <v>-183600000</v>
       </c>
       <c r="D3" t="n">
-        <v>223731458.33</v>
+        <v>296333300</v>
       </c>
       <c r="E3" t="n">
-        <v>-670999139.8099999</v>
+        <v>-598960246.29</v>
       </c>
       <c r="F3" t="n">
-        <v>1318160573.6</v>
+        <v>2550975998.33</v>
       </c>
       <c r="G3" t="n">
-        <v>2550975998.33</v>
+        <v>3222018234.91</v>
       </c>
       <c r="H3" t="n">
-        <v>4066822.14</v>
+        <v>32961474.18</v>
       </c>
       <c r="I3" t="n">
-        <v>-1236882246.87</v>
+        <v>-704003710.76</v>
       </c>
       <c r="J3" t="n">
-        <v>-705503993.95</v>
+        <v>-401500316.11</v>
       </c>
       <c r="K3" t="n">
-        <v>-19932204.39</v>
+        <v>-73026241.63</v>
       </c>
       <c r="L3" t="n">
-        <v>-549370655.3200001</v>
+        <v>-441196709.48</v>
       </c>
       <c r="M3" t="n">
-        <v>-134895175.02</v>
+        <v>112733300</v>
       </c>
       <c r="N3" t="n">
-        <v>-134895175.02</v>
+        <v>112733300</v>
       </c>
       <c r="O3" t="n">
-        <v>-358626633.35</v>
+        <v>-183600000</v>
       </c>
       <c r="P3" t="n">
-        <v>223731458.33</v>
+        <v>296333300</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1370820810.48</v>
+        <v>-1273308257.76</v>
       </c>
       <c r="R3" t="n">
-        <v>-700405215.63</v>
+        <v>-674934131.52</v>
       </c>
       <c r="S3" t="n">
-        <v>1440575207.42</v>
+        <v>696158576.67</v>
       </c>
       <c r="T3" t="n">
-        <v>-2140980423.05</v>
+        <v>-1371092708.19</v>
       </c>
       <c r="U3" t="n">
-        <v>-670415594.85</v>
+        <v>-598374126.24</v>
       </c>
       <c r="V3" t="n">
-        <v>583544.96</v>
+        <v>586120.05</v>
       </c>
       <c r="W3" t="n">
-        <v>-670999139.8099999</v>
+        <v>-598960246.29</v>
       </c>
       <c r="X3" t="n">
-        <v>839442557.5599999</v>
+        <v>970804863.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>-203029373.26</v>
+        <v>-141061648.57</v>
       </c>
       <c r="Z3" t="n">
-        <v>-13125962.6</v>
+        <v>20773413.64</v>
       </c>
       <c r="AA3" t="n">
-        <v>-245098249.74</v>
+        <v>41691122.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>51232885.38</v>
+        <v>-114110306.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>3961953.7</v>
+        <v>-89415878.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>47204683.86</v>
+        <v>41406314.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>345605755.48</v>
+        <v>320157679.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>209395231.84</v>
+        <v>177695637.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>136210523.64</v>
+        <v>142462042.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>-20389239.42</v>
+        <v>-42268543.77</v>
       </c>
       <c r="AI3" t="n">
-        <v>2336948.14</v>
+        <v>1280396.88</v>
       </c>
       <c r="AJ3" t="n">
-        <v>580828709.11</v>
+        <v>634365121.47</v>
       </c>
       <c r="AK3" t="n">
-        <v>839442557.5599999</v>
+        <v>970804863.11</v>
       </c>
       <c r="AL3" t="n">
-        <v>-406417277.01</v>
+        <v>-404251270.67</v>
       </c>
       <c r="AM3" t="n">
-        <v>-2417823517.04</v>
+        <v>-2299259599.53</v>
       </c>
       <c r="AN3" t="n">
-        <v>-953490076.24</v>
+        <v>-931860796.33</v>
       </c>
       <c r="AO3" t="n">
-        <v>-873645499.95</v>
+        <v>-762296200.71</v>
       </c>
       <c r="AP3" t="n">
-        <v>-590687940.85</v>
+        <v>-605102602.49</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3663683351.61</v>
+        <v>3674315733.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>173782970.54</v>
+        <v>165722792.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>3489900381.07</v>
+        <v>3508592941.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>371844616.82</v>
+        <v>168443417.75</v>
       </c>
       <c r="C4" t="n">
-        <v>-183600000</v>
+        <v>-358626633.35</v>
       </c>
       <c r="D4" t="n">
-        <v>296333300</v>
+        <v>223731458.33</v>
       </c>
       <c r="E4" t="n">
-        <v>-598960246.29</v>
+        <v>-670999139.8099999</v>
       </c>
       <c r="F4" t="n">
+        <v>1318160573.6</v>
+      </c>
+      <c r="G4" t="n">
         <v>2550975998.33</v>
       </c>
-      <c r="G4" t="n">
-        <v>3222018234.91</v>
-      </c>
       <c r="H4" t="n">
-        <v>32961474.18</v>
+        <v>4066822.14</v>
       </c>
       <c r="I4" t="n">
-        <v>-704003710.76</v>
+        <v>-1236882246.87</v>
       </c>
       <c r="J4" t="n">
-        <v>-401500316.11</v>
+        <v>-705503993.95</v>
       </c>
       <c r="K4" t="n">
-        <v>-73026241.63</v>
+        <v>-19932204.39</v>
       </c>
       <c r="L4" t="n">
-        <v>-441196709.48</v>
+        <v>-549370655.3200001</v>
       </c>
       <c r="M4" t="n">
-        <v>112733300</v>
+        <v>-134895175.02</v>
       </c>
       <c r="N4" t="n">
-        <v>112733300</v>
+        <v>-134895175.02</v>
       </c>
       <c r="O4" t="n">
-        <v>-183600000</v>
+        <v>-358626633.35</v>
       </c>
       <c r="P4" t="n">
-        <v>296333300</v>
+        <v>223731458.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1273308257.76</v>
+        <v>-1370820810.48</v>
       </c>
       <c r="R4" t="n">
-        <v>-674934131.52</v>
+        <v>-700405215.63</v>
       </c>
       <c r="S4" t="n">
-        <v>696158576.67</v>
+        <v>1440575207.42</v>
       </c>
       <c r="T4" t="n">
-        <v>-1371092708.19</v>
+        <v>-2140980423.05</v>
       </c>
       <c r="U4" t="n">
-        <v>-598374126.24</v>
+        <v>-670415594.85</v>
       </c>
       <c r="V4" t="n">
-        <v>586120.05</v>
+        <v>583544.96</v>
       </c>
       <c r="W4" t="n">
-        <v>-598960246.29</v>
+        <v>-670999139.8099999</v>
       </c>
       <c r="X4" t="n">
-        <v>970804863.11</v>
+        <v>839442557.5599999</v>
       </c>
       <c r="Y4" t="n">
-        <v>-141061648.57</v>
+        <v>-203029373.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>20773413.64</v>
+        <v>-13125962.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>41691122.55</v>
+        <v>-245098249.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>-114110306.57</v>
+        <v>51232885.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>-89415878.19</v>
+        <v>3961953.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>41406314.44</v>
+        <v>47204683.86</v>
       </c>
       <c r="AE4" t="n">
-        <v>320157679.7</v>
+        <v>345605755.48</v>
       </c>
       <c r="AF4" t="n">
-        <v>177695637.25</v>
+        <v>209395231.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>142462042.45</v>
+        <v>136210523.64</v>
       </c>
       <c r="AH4" t="n">
-        <v>-42268543.77</v>
+        <v>-20389239.42</v>
       </c>
       <c r="AI4" t="n">
-        <v>1280396.88</v>
+        <v>2336948.14</v>
       </c>
       <c r="AJ4" t="n">
-        <v>634365121.47</v>
+        <v>580828709.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>970804863.11</v>
+        <v>839442557.5599999</v>
       </c>
       <c r="AL4" t="n">
-        <v>-404251270.67</v>
+        <v>-406417277.01</v>
       </c>
       <c r="AM4" t="n">
-        <v>-2299259599.53</v>
+        <v>-2417823517.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>-931860796.33</v>
+        <v>-953490076.24</v>
       </c>
       <c r="AO4" t="n">
-        <v>-762296200.71</v>
+        <v>-873645499.95</v>
       </c>
       <c r="AP4" t="n">
-        <v>-605102602.49</v>
+        <v>-590687940.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3674315733.31</v>
+        <v>3663683351.61</v>
       </c>
       <c r="AR4" t="n">
-        <v>165722792.1</v>
+        <v>173782970.54</v>
       </c>
       <c r="AS4" t="n">
-        <v>3508592941.21</v>
+        <v>3489900381.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>702477754.28</v>
+        <v>561445148.23</v>
       </c>
       <c r="C5" t="n">
-        <v>-639517504</v>
+        <v>-39838124.98</v>
       </c>
       <c r="D5" t="n">
-        <v>303900000</v>
+        <v>119296750.01</v>
       </c>
       <c r="E5" t="n">
-        <v>-482500771.37</v>
+        <v>-624813272.52</v>
       </c>
       <c r="F5" t="n">
-        <v>3222018234.91</v>
+        <v>1104655208.72</v>
       </c>
       <c r="G5" t="n">
-        <v>865134656.27</v>
+        <v>1318160573.6</v>
       </c>
       <c r="H5" t="n">
-        <v>-6774739.78</v>
+        <v>3947050.81</v>
       </c>
       <c r="I5" t="n">
-        <v>2363658318.42</v>
+        <v>-217452415.69</v>
       </c>
       <c r="J5" t="n">
-        <v>1548327729.35</v>
+        <v>121841261.13</v>
       </c>
       <c r="K5" t="n">
-        <v>1900389917.95</v>
+        <v>588417878.22</v>
       </c>
       <c r="L5" t="n">
-        <v>-15543344.67</v>
+        <v>-546035242.12</v>
       </c>
       <c r="M5" t="n">
-        <v>-335617504</v>
+        <v>79458625.03</v>
       </c>
       <c r="N5" t="n">
-        <v>-335617504</v>
+        <v>79458625.03</v>
       </c>
       <c r="O5" t="n">
-        <v>-639517504</v>
+        <v>-39838124.98</v>
       </c>
       <c r="P5" t="n">
-        <v>303900000</v>
+        <v>119296750.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>-369647936.58</v>
+        <v>-1525552097.57</v>
       </c>
       <c r="R5" t="n">
-        <v>111260230.7</v>
+        <v>-901381028.14</v>
       </c>
       <c r="S5" t="n">
-        <v>609339253.7</v>
+        <v>2458983104.06</v>
       </c>
       <c r="T5" t="n">
-        <v>-498079023</v>
+        <v>-3360364132.2</v>
       </c>
       <c r="U5" t="n">
-        <v>-480908167.28</v>
+        <v>-624171069.4299999</v>
       </c>
       <c r="V5" t="n">
-        <v>1592604.09</v>
+        <v>642203.09</v>
       </c>
       <c r="W5" t="n">
-        <v>-482500771.37</v>
+        <v>-624813272.52</v>
       </c>
       <c r="X5" t="n">
-        <v>1184978525.65</v>
+        <v>1186258420.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>297411490.89</v>
+        <v>8617876.300000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>-3571070.19</v>
+        <v>-55904655.09</v>
       </c>
       <c r="AA5" t="n">
-        <v>277538888.44</v>
+        <v>178499956.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>-46530969.49</v>
+        <v>-56401484.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>69974642.13</v>
+        <v>-57575940.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>30682385.85</v>
+        <v>14664087.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>304268219.64</v>
+        <v>376231728.48</v>
       </c>
       <c r="AF5" t="n">
-        <v>173484287.18</v>
+        <v>242130104.88</v>
       </c>
       <c r="AG5" t="n">
-        <v>130783932.46</v>
+        <v>134101623.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>-134237582.59</v>
+        <v>-47950017.61</v>
       </c>
       <c r="AI5" t="n">
-        <v>3646380.16</v>
+        <v>2301927.42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>528321518.79</v>
+        <v>605155649.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1184978525.65</v>
+        <v>1186258420.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>-324111772.31</v>
+        <v>-455262933.57</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1924645359.17</v>
+        <v>-2678727351.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>-689931181.13</v>
+        <v>-1114619849.24</v>
       </c>
       <c r="AO5" t="n">
-        <v>-740661494.34</v>
+        <v>-962503788.6900001</v>
       </c>
       <c r="AP5" t="n">
-        <v>-494052683.7</v>
+        <v>-601603713.36</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3433735657.13</v>
+        <v>4320248705.61</v>
       </c>
       <c r="AR5" t="n">
-        <v>153664993.64</v>
+        <v>178101687.22</v>
       </c>
       <c r="AS5" t="n">
-        <v>3280070663.49</v>
+        <v>4142147018.39</v>
       </c>
     </row>
   </sheetData>
@@ -3366,7 +3366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU2"/>
+  <dimension ref="A1:EW2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3782,345 +3782,355 @@
       </c>
       <c r="CE1" t="inlineStr">
         <is>
+          <t>recommendationMean</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4212,34 +4222,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>32.54</v>
+        <v>30.38</v>
       </c>
       <c r="T2" t="n">
-        <v>36.25</v>
+        <v>30.23</v>
       </c>
       <c r="U2" t="n">
-        <v>32.5</v>
+        <v>29.25</v>
       </c>
       <c r="V2" t="n">
-        <v>34.15</v>
+        <v>30.8</v>
       </c>
       <c r="W2" t="n">
-        <v>32.54</v>
+        <v>30.38</v>
       </c>
       <c r="X2" t="n">
-        <v>36.25</v>
+        <v>30.23</v>
       </c>
       <c r="Y2" t="n">
-        <v>32.5</v>
+        <v>29.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>34.15</v>
+        <v>30.8</v>
       </c>
       <c r="AA2" t="n">
         <v>0.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AC2" t="n">
         <v>1779753600</v>
@@ -4251,34 +4261,34 @@
         <v>2.51</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.021</v>
+        <v>-0.164</v>
       </c>
       <c r="AG2" t="n">
-        <v>55.699993</v>
+        <v>51.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>52.21875</v>
+        <v>48.093754</v>
       </c>
       <c r="AI2" t="n">
-        <v>25553320</v>
+        <v>19349745</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25553320</v>
+        <v>19349745</v>
       </c>
       <c r="AK2" t="n">
-        <v>15986010</v>
+        <v>17731823</v>
       </c>
       <c r="AL2" t="n">
-        <v>22701418</v>
+        <v>16910962</v>
       </c>
       <c r="AM2" t="n">
-        <v>22701418</v>
+        <v>16910962</v>
       </c>
       <c r="AN2" t="n">
-        <v>33.45</v>
+        <v>30.79</v>
       </c>
       <c r="AO2" t="n">
-        <v>33.46</v>
+        <v>30.8</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -4287,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>37257166848</v>
+        <v>34314053632</v>
       </c>
       <c r="AS2" t="n">
-        <v>37257168599</v>
+        <v>33868126333</v>
       </c>
       <c r="AT2" t="n">
-        <v>32.19</v>
+        <v>29.25</v>
       </c>
       <c r="AU2" t="n">
         <v>70.98999999999999</v>
@@ -4305,19 +4315,19 @@
         <v>6.72743</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.244751000000001</v>
+        <v>7.593461</v>
       </c>
       <c r="AY2" t="n">
-        <v>51.3464</v>
+        <v>42.9442</v>
       </c>
       <c r="AZ2" t="n">
-        <v>53.91775</v>
+        <v>52.3667</v>
       </c>
       <c r="BA2" t="n">
         <v>0.55</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.016902274</v>
+        <v>0.018104017</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4328,13 +4338,13 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>35792764928</v>
+        <v>32849649664</v>
       </c>
       <c r="BF2" t="n">
         <v>0.14969</v>
       </c>
       <c r="BG2" t="n">
-        <v>452013512</v>
+        <v>445101650</v>
       </c>
       <c r="BH2" t="n">
         <v>1114816535</v>
@@ -4343,7 +4353,7 @@
         <v>0.61522996</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.13708</v>
+        <v>0.13701001</v>
       </c>
       <c r="BK2" t="n">
         <v>1114816535</v>
@@ -4352,7 +4362,7 @@
         <v>8.206</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.0726295</v>
+        <v>3.7509139</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4384,16 +4394,16 @@
         <v>1429833600</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.921</v>
+        <v>7.269</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.595</v>
+        <v>30.832</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.26500988</v>
+        <v>-0.36918604</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="CA2" t="n">
         <v>0.55</v>
@@ -4407,253 +4417,261 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CF2" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>strong_buy</t>
+        </is>
+      </c>
+      <c r="CG2" t="n">
         <v>1826301056</v>
       </c>
-      <c r="CG2" t="n">
+      <c r="CH2" t="n">
         <v>1.638</v>
       </c>
-      <c r="CH2" t="n">
+      <c r="CI2" t="n">
         <v>1065423488</v>
       </c>
-      <c r="CI2" t="n">
+      <c r="CJ2" t="n">
         <v>240210912</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CK2" t="n">
         <v>1.513</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>2.336</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>4518895104</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>2.591</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>4.011</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>0.03798</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
         <v>0.07414</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>3388284928</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CS2" t="n">
         <v>77718200</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CT2" t="n">
         <v>1068320832</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
         <v>0.111</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="n">
         <v>0.157</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CW2" t="n">
         <v>0.7498</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CX2" t="n">
         <v>0.23577</v>
       </c>
-      <c r="CX2" t="n">
+      <c r="CY2" t="n">
         <v>0.20059</v>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>002294.SZ</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DE2" t="b">
+      <c r="DF2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="n">
+        <v>0.40000153</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>29.25 - 30.8</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>17731823</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1.5300007</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.052307718</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>29.25 - 70.99</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>-40.21</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.5664178</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-36.918606</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1745319540</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1745319540</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1744268400</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1744268400</v>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1252546200000</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1.3166608</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-12.164198</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.2832559</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-21.586699</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.41222188</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>1.0 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EL2" t="n">
+        <v>1782111882</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>finmb_48784795</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="EQ2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="ES2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET2" t="inlineStr">
         <is>
           <t>SHENZHEN SALUBRIS PHARMA CO LTD</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="EU2" t="inlineStr">
         <is>
           <t>Shenzhen Salubris Pharmaceuticals Co., Ltd.</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>2.7043552</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>1780038255</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>finmb_48784795</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1252546200000</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.87999725</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>32.5 - 34.15</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>15986010</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1.2299995</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.03821061</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>32.19 - 70.99</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>-37.57</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.52922946</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-26.500988</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1745319540</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1745319540</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1744268400</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1744268400</v>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-17.926403</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>-0.34912676</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>-20.497753</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.38016707</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ET2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EU2" t="inlineStr"/>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
